--- a/data/trending_integrated_20261016_10.xlsx
+++ b/data/trending_integrated_20261016_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8020</v>
+        <v>8060</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.07%</t>
+          <t>'+22.68%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H2" t="n">
         <v>0.73</v>
@@ -610,7 +610,7 @@
         <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>49673564490</v>
+        <v>51402763380</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>군공항 이전 이슈, 신고가 돌파 시 8만원 가능성 언급. 투자경고 종목임에도 급등 기대감 표현 및 수급 확인.</t>
+          <t>군공항 이전 관련 호재 및 호남 반도체 건설주 테마 상승 기대감. 외국인 수급 전환 가능성 및 투자 경고 종목 지정에도 상승 여력 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['군공항', '신고가', '투자경고']</t>
+          <t>['군공항', '호남반도체', '수급']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8320</v>
+        <v>8480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.36%</t>
+          <t>'+18.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
         <v>0.72</v>
@@ -702,7 +702,7 @@
         <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>87597940915</v>
+        <v>99326752680</v>
       </c>
       <c r="P3" t="n">
         <v>8600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>뉴로메가 편입 사례를 들며 HT로보틱스의 높은 상승 가능성을 언급. 10만원 목표가 제시 및 신고가 기대감 표현.</t>
+          <t>HT로보틱스의 높은 편입 종목 수와 실적 대비 저평가 가능성에 따른 텐버거 기대감. 신고가 및 10만원 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['뉴로메가', '텐버거', '신고가']</t>
+          <t>['로봇', '텐버거', '실적']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18270</v>
+        <v>9860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+11.54%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17470</v>
+        <v>8840</v>
       </c>
       <c r="K4" t="n">
-        <v>18710</v>
+        <v>9030</v>
       </c>
       <c r="L4" t="n">
-        <v>20300</v>
+        <v>10690</v>
       </c>
       <c r="M4" t="n">
-        <v>17630</v>
+        <v>8610</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>14.37</v>
       </c>
       <c r="O4" t="n">
-        <v>110640501800</v>
+        <v>61231971290</v>
       </c>
       <c r="P4" t="n">
-        <v>28800</v>
+        <v>14350</v>
       </c>
       <c r="Q4" t="n">
-        <v>15780</v>
+        <v>465</v>
       </c>
       <c r="R4" t="n">
-        <v>16000</v>
+        <v>-110000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 테마 및 일본/호남 공장 수혜주로 언급하나, 단일계좌 투매 및 급락 패턴에 대한 우려 표출. 매도 권유.</t>
+          <t>호남반도체 클러스터 사업 및 국책사업 관련 기대감 속 일부 투자자 매수세 유입. 다만, 데드캣 바운스 및 종가 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '단일계좌', '급락']</t>
+          <t>['국책사업', '반도체', '매집']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15130</v>
+        <v>18350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+5.04%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="H5" t="n">
-        <v>9.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14670</v>
+        <v>17470</v>
       </c>
       <c r="K5" t="n">
-        <v>14800</v>
+        <v>18710</v>
       </c>
       <c r="L5" t="n">
-        <v>15270</v>
+        <v>20300</v>
       </c>
       <c r="M5" t="n">
-        <v>14800</v>
+        <v>17630</v>
       </c>
       <c r="N5" t="n">
-        <v>9.710000000000001</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>13741230010</v>
+        <v>113516051955</v>
       </c>
       <c r="P5" t="n">
-        <v>40350</v>
+        <v>28800</v>
       </c>
       <c r="Q5" t="n">
-        <v>3320</v>
+        <v>15780</v>
       </c>
       <c r="R5" t="n">
-        <v>-47000</v>
+        <v>16000</v>
       </c>
       <c r="S5" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이재명 대통령 및 금감원, 사모펀드, 뱅크런 등 정치 경제적 이슈와 관련된 부정적이고 반복적인 언급이 다수.</t>
+          <t>일본 및 호남 메가 반도체 공장 수혜주로 언급되나, 단일 계좌 및 투기 종목 지정으로 인한 급락 가능성 제기. 반도체 테마 전반의 약세 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['이재명', '금감원', '뱅크런']</t>
+          <t>['반도체', '수혜주', '단일계좌']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1299000</v>
+        <v>15600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.93%</t>
+          <t>'+4.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>553</v>
+        <v>51</v>
       </c>
       <c r="G6" t="n">
-        <v>1319</v>
+        <v>121</v>
       </c>
       <c r="H6" t="n">
-        <v>48.85</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1262000</v>
+        <v>14940</v>
       </c>
       <c r="K6" t="n">
-        <v>1290000</v>
+        <v>14940</v>
       </c>
       <c r="L6" t="n">
-        <v>1300000</v>
+        <v>16290</v>
       </c>
       <c r="M6" t="n">
-        <v>1247000</v>
+        <v>14330</v>
       </c>
       <c r="N6" t="n">
-        <v>49.02</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1911275026500</v>
+        <v>24887675585</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>30800</v>
       </c>
       <c r="Q6" t="n">
-        <v>420500</v>
+        <v>9810</v>
       </c>
       <c r="R6" t="n">
-        <v>-291000</v>
+        <v>19000</v>
       </c>
       <c r="S6" t="n">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>이재명 정부 및 최태원 회장 관련 부정적 언급, 오너 리스크와 솔리다임 상장 계획에 대한 비판이 주를 이룸. 주가 하락에 대한 불만 표출.</t>
+          <t>상장 사기 의혹 및 코넥스에서의 주가 띄우기 후 매도 가능성에 대한 강한 의심. 시총 대비 공모가 고평가 지적.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['이재명', '최태원', '솔리다임']</t>
+          <t>['상장사기', '코넥스', '조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64900</v>
+        <v>15130</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>309</v>
+        <v>88</v>
       </c>
       <c r="H7" t="n">
-        <v>22.1</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>63300</v>
+        <v>14670</v>
       </c>
       <c r="K7" t="n">
-        <v>63900</v>
+        <v>14800</v>
       </c>
       <c r="L7" t="n">
-        <v>65500</v>
+        <v>15270</v>
       </c>
       <c r="M7" t="n">
-        <v>63500</v>
+        <v>14800</v>
       </c>
       <c r="N7" t="n">
-        <v>22.11</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>52977472850</v>
+        <v>14845610280</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>64000</v>
+        <v>-47000</v>
       </c>
       <c r="S7" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정부 정책 및 금융 당국(이억원, 금감원)에 대한 비판, 원전주 및 뉴스케일파워 등 타 종목 언급, 송기훈 애널리스트 관련 부정적 평가.</t>
+          <t>정치적 이슈(이재명 대통령)와 연계된 주가 조작 및 뱅크런에 대한 반복적인 언급. 구체적인 팩트 기반 분석 부재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['정부', '금감원', '원전주']</t>
+          <t>['주가조작', '뱅크런', '금감원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>215000</v>
+        <v>1296000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.38%</t>
+          <t>'+2.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="E8" t="n">
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>503</v>
+        <v>557</v>
       </c>
       <c r="G8" t="n">
-        <v>1327</v>
+        <v>1312</v>
       </c>
       <c r="H8" t="n">
-        <v>45.98</v>
+        <v>48.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>210000</v>
+        <v>1262000</v>
       </c>
       <c r="K8" t="n">
-        <v>215000</v>
+        <v>1290000</v>
       </c>
       <c r="L8" t="n">
-        <v>215500</v>
+        <v>1301000</v>
       </c>
       <c r="M8" t="n">
-        <v>210500</v>
+        <v>1247000</v>
       </c>
       <c r="N8" t="n">
-        <v>46.16</v>
+        <v>49.02</v>
       </c>
       <c r="O8" t="n">
-        <v>999773450000</v>
+        <v>2050474576000</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>420500</v>
       </c>
       <c r="R8" t="n">
-        <v>-865000</v>
+        <v>-291000</v>
       </c>
       <c r="S8" t="n">
-        <v>111000</v>
+        <v>58000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재명 정부 및 노조 관련 정치적 언급이 많으며, 외인 매도세 지속 및 프로그램 매도 현상 관찰됨.</t>
+          <t>솔리다임 상장 계획 및 오너 리스크에 대한 부정적 전망. 가짜 반등 및 개미 꼬시기 가능성 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['이재명', '노조', '외인매도']</t>
+          <t>['솔리다임', '오너리스크', '반도체']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41100</v>
+        <v>215250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.86%</t>
+          <t>'+2.50%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="E9" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>96</v>
+        <v>504</v>
       </c>
       <c r="G9" t="n">
-        <v>592</v>
+        <v>1285</v>
       </c>
       <c r="H9" t="n">
-        <v>12.97</v>
+        <v>45.98</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>40750</v>
+        <v>210000</v>
       </c>
       <c r="K9" t="n">
-        <v>40600</v>
+        <v>215000</v>
       </c>
       <c r="L9" t="n">
-        <v>41450</v>
+        <v>215500</v>
       </c>
       <c r="M9" t="n">
-        <v>40050</v>
+        <v>210500</v>
       </c>
       <c r="N9" t="n">
-        <v>12.84</v>
+        <v>46.16</v>
       </c>
       <c r="O9" t="n">
-        <v>5743251225</v>
+        <v>1110309349250</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-4000</v>
+        <v>-865000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 기대감과 함께 야간 선물 상승 및 외인 매수세 언급. 환희에 팔라는 경고도 존재.</t>
+          <t>정권 교체 및 정치적 이슈와 연계된 부정적 언급 다수. 외인 매도세 및 프로그램 매도에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA승인', '야간선물', '외인매수']</t>
+          <t>['정치', '외인매도', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14480</v>
+        <v>41200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'+1.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>108</v>
+        <v>606</v>
       </c>
       <c r="H10" t="n">
-        <v>0.11</v>
+        <v>12.97</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14940</v>
+        <v>40750</v>
       </c>
       <c r="K10" t="n">
-        <v>14940</v>
+        <v>40600</v>
       </c>
       <c r="L10" t="n">
-        <v>16290</v>
+        <v>41450</v>
       </c>
       <c r="M10" t="n">
-        <v>14330</v>
+        <v>40050</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>12.84</v>
       </c>
       <c r="O10" t="n">
-        <v>21047824225</v>
+        <v>6029171700</v>
       </c>
       <c r="P10" t="n">
-        <v>30800</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>9810</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>19000</v>
+        <v>-4000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>상장 사기 의혹 제기, 코넥스 주가 띄우기 후 코스닥 상장 시 매도 패턴 지적. 김임준 대표 사퇴 요구 및 주가 조작 주장.</t>
+          <t>담관암 FDA 승인 기대감과 함께 야간 선물 상승 및 외인 매수세 언급. 환희에 팔라는 경고도 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['상장사기', '코넥스', '주가조작']</t>
+          <t>['FDA승인', '야간선물', '외인매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>2.5</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
         <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H11" t="n">
         <v>4.28</v>
@@ -1438,7 +1438,7 @@
         <v>1.78</v>
       </c>
       <c r="O11" t="n">
-        <v>28242211325</v>
+        <v>28975396775</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>해킹 사고 증가에 따른 보안주 부각 가능성 언급. 농협, KDB 방어 성공 후 신규 납품 요청 쇄도 소식 기반 상승 기대.</t>
+          <t>금융권 해킹 시도 증가에 따른 보안 솔루션 수요 증가 기대. 농협, KDB 납품 및 신규 납품 요청 증가 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1477,6 +1477,190 @@
       <c r="Z11" t="inlineStr">
         <is>
           <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>28150</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-4.41%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" t="n">
+        <v>132</v>
+      </c>
+      <c r="H12" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>29450</v>
+      </c>
+      <c r="K12" t="n">
+        <v>29450</v>
+      </c>
+      <c r="L12" t="n">
+        <v>29600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>27600</v>
+      </c>
+      <c r="N12" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>51022804425</v>
+      </c>
+      <c r="P12" t="n">
+        <v>32500</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>21000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-57000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>실적 발표 후 급락에 대한 실망감과 외인 매도세 지속에 대한 우려. 유튜버 및 개인 투자 의견에 대한 불신 표출.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['실적', '외인매도', '개폭락']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>003490</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>65000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-5.66%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E13" t="n">
+        <v>95</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57</v>
+      </c>
+      <c r="G13" t="n">
+        <v>319</v>
+      </c>
+      <c r="H13" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>68900</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="O13" t="n">
+        <v>55790000000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>64000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>정부 정책 및 금융 당국(이억원, 금감원)에 대한 비판, 원전주 및 뉴스케일파워 등 타 종목 언급, 송기훈 애널리스트 관련 부정적 평가.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['정부', '금감원', '원전주']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>034020</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261016_10.xlsx
+++ b/data/trending_integrated_20261016_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8060</v>
+        <v>8160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.68%</t>
+          <t>'+24.20%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H2" t="n">
         <v>0.73</v>
@@ -610,7 +610,7 @@
         <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>51402763380</v>
+        <v>57159219150</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 호재 및 호남 반도체 건설주 테마 상승 기대감. 외국인 수급 전환 가능성 및 투자 경고 종목 지정에도 상승 여력 언급.</t>
+          <t>군공항 이전 및 호남 반도체 관련 호재 언급하며 주가 급등 기대감 표출. 개인 투자자들의 심리를 이용한 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['군공항', '호남반도체', '수급']</t>
+          <t>['군공항', '호남반도체', '상한가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8480</v>
+        <v>8390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.60%</t>
+          <t>'+17.34%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="H3" t="n">
         <v>0.72</v>
@@ -702,7 +702,7 @@
         <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>99326752680</v>
+        <v>104102525845</v>
       </c>
       <c r="P3" t="n">
         <v>8600</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HT로보틱스의 높은 편입 종목 수와 실적 대비 저평가 가능성에 따른 텐버거 기대감. 신고가 및 10만원 가능성 언급.</t>
+          <t>로봇 관련 사업 확장 및 인수합병 기대감으로 주가 급등 전망. 뉴로메가 비교 및 텐버거 가능성 언급하며 강한 긍정적 논조.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '텐버거', '실적']</t>
+          <t>['로봇', '인수합병', '텐버거']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9860</v>
+        <v>10070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.54%</t>
+          <t>'+13.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.77</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H4" t="n">
         <v>13.6</v>
@@ -794,7 +794,7 @@
         <v>14.37</v>
       </c>
       <c r="O4" t="n">
-        <v>61231971290</v>
+        <v>67738475355</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>호남반도체 클러스터 사업 및 국책사업 관련 기대감 속 일부 투자자 매수세 유입. 다만, 데드캣 바운스 및 종가 급락 가능성 언급.</t>
+          <t>국책사업 및 반도체 관련 호재 언급과 함께 주가 상승 기대감 표출. 다만, 데드캣 바운스 및 종가 급락 가능성 언급으로 불확실성 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국책사업', '반도체', '매집']</t>
+          <t>['국책사업', '반도체', '박스권']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18350</v>
+        <v>18300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.04%</t>
+          <t>'+4.75%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>113516051955</v>
+        <v>115838690030</v>
       </c>
       <c r="P5" t="n">
         <v>28800</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>일본 및 호남 메가 반도체 공장 수혜주로 언급되나, 단일 계좌 및 투기 종목 지정으로 인한 급락 가능성 제기. 반도체 테마 전반의 약세 우려.</t>
+          <t>반도체 테마 관련 수혜주 언급에도 불구하고, 단일 계좌 및 투주 등으로 인한 주가 하락 가능성 경고. 매도 권유.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '수혜주', '단일계좌']</t>
+          <t>['반도체', '단일계좌', '투주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15600</v>
+        <v>13590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.42%</t>
+          <t>'+4.06%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>3.42</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14940</v>
+        <v>13060</v>
       </c>
       <c r="K6" t="n">
-        <v>14940</v>
+        <v>13390</v>
       </c>
       <c r="L6" t="n">
-        <v>16290</v>
+        <v>13620</v>
       </c>
       <c r="M6" t="n">
-        <v>14330</v>
+        <v>12910</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O6" t="n">
-        <v>24887675585</v>
+        <v>27450541610</v>
       </c>
       <c r="P6" t="n">
-        <v>30800</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>9810</v>
+        <v>1640</v>
       </c>
       <c r="R6" t="n">
-        <v>19000</v>
+        <v>-48000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>상장 사기 의혹 및 코넥스에서의 주가 띄우기 후 매도 가능성에 대한 강한 의심. 시총 대비 공모가 고평가 지적.</t>
+          <t>야간선물 및 미국장 반등, 광통신 테마 수혜 기대감 언급. 다만, 한국 증시 문제점 및 미장 약세 관련 언급으로 불확실성 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['상장사기', '코넥스', '조작']</t>
+          <t>['광통신', '야간선물', '수주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15130</v>
+        <v>15150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+3.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
         <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>9.779999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>14845610280</v>
+        <v>16395906235</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈(이재명 대통령)와 연계된 주가 조작 및 뱅크런에 대한 반복적인 언급. 구체적인 팩트 기반 분석 부재.</t>
+          <t>정치적 이슈 및 주가 조작 관련 의혹 제기가 반복적으로 나타남. 뱅크런 및 사모펀드 점검 관련 언급으로 시장 불안감 표출.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가조작', '뱅크런', '금감원']</t>
+          <t>['주가조작', '이재명', '뱅크런']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1296000</v>
+        <v>65300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.69%</t>
+          <t>'+3.16%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.17</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>557</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>1312</v>
+        <v>330</v>
       </c>
       <c r="H8" t="n">
-        <v>48.85</v>
+        <v>22.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1262000</v>
+        <v>63300</v>
       </c>
       <c r="K8" t="n">
-        <v>1290000</v>
+        <v>63900</v>
       </c>
       <c r="L8" t="n">
-        <v>1301000</v>
+        <v>65700</v>
       </c>
       <c r="M8" t="n">
-        <v>1247000</v>
+        <v>63500</v>
       </c>
       <c r="N8" t="n">
-        <v>49.02</v>
+        <v>22.11</v>
       </c>
       <c r="O8" t="n">
-        <v>2050474576000</v>
+        <v>62489149500</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>420500</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>-291000</v>
+        <v>64000</v>
       </c>
       <c r="S8" t="n">
-        <v>58000</v>
+        <v>5000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>솔리다임 상장 계획 및 오너 리스크에 대한 부정적 전망. 가짜 반등 및 개미 꼬시기 가능성 제기.</t>
+          <t>뉴스케일파워 등 관련 뉴스와 함께 주가 상승 기대감 표출. 다만, 3분기 매출 하회 및 외국계 증권사 매도 관련 언급으로 불확실성 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '오너리스크', '반도체']</t>
+          <t>['뉴스케일파워', '원전주', '매출하회']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>215250</v>
+        <v>216000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.50%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G9" t="n">
-        <v>1285</v>
+        <v>1255</v>
       </c>
       <c r="H9" t="n">
         <v>45.98</v>
@@ -1245,7 +1245,7 @@
         <v>215000</v>
       </c>
       <c r="L9" t="n">
-        <v>215500</v>
+        <v>217500</v>
       </c>
       <c r="M9" t="n">
         <v>210500</v>
@@ -1254,7 +1254,7 @@
         <v>46.16</v>
       </c>
       <c r="O9" t="n">
-        <v>1110309349250</v>
+        <v>1245480082000</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정권 교체 및 정치적 이슈와 연계된 부정적 언급 다수. 외인 매도세 및 프로그램 매도에 대한 우려 제기.</t>
+          <t>정치적 이슈 및 노조 관련 언급이 주를 이루며, 주가 하락에 대한 부정적 전망과 개미 투자자들의 불안 심리 반영. 외인 매도세 지속 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치', '외인매도', '반도체']</t>
+          <t>['이재명', '외인매도', '주주제도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41200</v>
+        <v>1294000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.10%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>157</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>553</v>
       </c>
       <c r="G10" t="n">
-        <v>606</v>
+        <v>1280</v>
       </c>
       <c r="H10" t="n">
-        <v>12.97</v>
+        <v>48.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>40750</v>
+        <v>1262000</v>
       </c>
       <c r="K10" t="n">
-        <v>40600</v>
+        <v>1290000</v>
       </c>
       <c r="L10" t="n">
-        <v>41450</v>
+        <v>1308000</v>
       </c>
       <c r="M10" t="n">
-        <v>40050</v>
+        <v>1247000</v>
       </c>
       <c r="N10" t="n">
-        <v>12.84</v>
+        <v>49.02</v>
       </c>
       <c r="O10" t="n">
-        <v>6029171700</v>
+        <v>2188369515500</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>420500</v>
       </c>
       <c r="R10" t="n">
-        <v>-4000</v>
+        <v>-291000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 기대감과 함께 야간 선물 상승 및 외인 매수세 언급. 환희에 팔라는 경고도 존재.</t>
+          <t>정치적 이슈와 맞물려 주가 하락에 대한 부정적 전망 강하게 제기. 솔리다임 관련 언급과 함께 오너 리스크 부각.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA승인', '야간선물', '외인매수']</t>
+          <t>['이재명', '솔리다임', '오너리스크']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20100</v>
+        <v>15200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>111</v>
+      </c>
+      <c r="F11" t="n">
         <v>57</v>
       </c>
-      <c r="F11" t="n">
-        <v>43</v>
-      </c>
       <c r="G11" t="n">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="H11" t="n">
-        <v>4.28</v>
+        <v>0.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>20750</v>
+        <v>14940</v>
       </c>
       <c r="K11" t="n">
-        <v>20500</v>
+        <v>14940</v>
       </c>
       <c r="L11" t="n">
-        <v>21500</v>
+        <v>16290</v>
       </c>
       <c r="M11" t="n">
-        <v>19440</v>
+        <v>14330</v>
       </c>
       <c r="N11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>28975396775</v>
+        <v>31737012710</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>30800</v>
       </c>
       <c r="Q11" t="n">
-        <v>6320</v>
+        <v>9810</v>
       </c>
       <c r="R11" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>금융권 해킹 시도 증가에 따른 보안 솔루션 수요 증가 기대. 농협, KDB 납품 및 신규 납품 요청 증가 언급.</t>
+          <t>코넥스 상장 사기 의혹 제기, 무능한 경영진 비판 및 주가 급락 기원.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '납품']</t>
+          <t>['상장 사기', '경영진', '주가 급락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28150</v>
+        <v>41250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'+1.23%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="G12" t="n">
-        <v>132</v>
+        <v>645</v>
       </c>
       <c r="H12" t="n">
-        <v>53.61</v>
+        <v>12.97</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29450</v>
+        <v>40750</v>
       </c>
       <c r="K12" t="n">
-        <v>29450</v>
+        <v>40600</v>
       </c>
       <c r="L12" t="n">
-        <v>29600</v>
+        <v>41450</v>
       </c>
       <c r="M12" t="n">
-        <v>27600</v>
+        <v>40050</v>
       </c>
       <c r="N12" t="n">
-        <v>26.75</v>
+        <v>12.84</v>
       </c>
       <c r="O12" t="n">
-        <v>51022804425</v>
+        <v>6317045550</v>
       </c>
       <c r="P12" t="n">
-        <v>32500</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>21000</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>-9000</v>
+        <v>-4000</v>
       </c>
       <c r="S12" t="n">
-        <v>-57000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>실적 발표 후 급락에 대한 실망감과 외인 매도세 지속에 대한 우려. 유튜버 및 개인 투자 의견에 대한 불신 표출.</t>
+          <t>HLB 담관암 FDA 승인 기대감 속, 진양곤 회장 및 경영진에 대한 불신 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['실적', '외인매도', '개폭락']</t>
+          <t>['FDA 승인', '담관암', '진양곤 회장']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,86 +1568,86 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65000</v>
+        <v>20400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.66%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="F13" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>319</v>
+        <v>154</v>
       </c>
       <c r="H13" t="n">
-        <v>22.1</v>
+        <v>4.28</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>68900</v>
+        <v>20750</v>
       </c>
       <c r="K13" t="n">
+        <v>20500</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21500</v>
+      </c>
+      <c r="M13" t="n">
+        <v>19440</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O13" t="n">
+        <v>29725690375</v>
+      </c>
+      <c r="P13" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>6320</v>
+      </c>
+      <c r="R13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>22.11</v>
-      </c>
-      <c r="O13" t="n">
-        <v>55790000000</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>64000</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5000</v>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정부 정책 및 금융 당국(이억원, 금감원)에 대한 비판, 원전주 및 뉴스케일파워 등 타 종목 언급, 송기훈 애널리스트 관련 부정적 평가.</t>
+          <t>라온시큐어, 보안 이슈 속 신규 납품 요청 및 연기금 매수세 기대, 목표가 제시.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정부', '금감원', '원전주']</t>
+          <t>['보안', '납품 요청', '연기금']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,7 +1660,99 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>28050</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-4.75%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>44</v>
+      </c>
+      <c r="F14" t="n">
+        <v>38</v>
+      </c>
+      <c r="G14" t="n">
+        <v>183</v>
+      </c>
+      <c r="H14" t="n">
+        <v>53.59</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>29450</v>
+      </c>
+      <c r="K14" t="n">
+        <v>29450</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>27600</v>
+      </c>
+      <c r="N14" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>55431561625</v>
+      </c>
+      <c r="P14" t="n">
+        <v>32500</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>21000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-57000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>실적 발표 후 주가 급락 및 외인 매도 시작에 대한 우려 제기. 유튜버 및 타인 의견 불신하며 매도 권유.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['실적발표', '외인매도', '폭락']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>003490</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261016_10.xlsx
+++ b/data/trending_integrated_20261016_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8160</v>
+        <v>8080</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+24.20%</t>
+          <t>'+22.98%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H2" t="n">
         <v>0.73</v>
@@ -610,7 +610,7 @@
         <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>57159219150</v>
+        <v>58948698370</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>군공항 이전 및 호남 반도체 관련 호재 언급하며 주가 급등 기대감 표출. 개인 투자자들의 심리를 이용한 상승 가능성 언급.</t>
+          <t>군공항 이전 관련 호재 및 정치적 불확실성 언급. 호남 반도체 관련주 동반 상승 가능성 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['군공항', '호남반도체', '상한가']</t>
+          <t>['군공항', '호남반도체', '정치']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8390</v>
+        <v>8430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.34%</t>
+          <t>'+17.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="H3" t="n">
         <v>0.72</v>
@@ -702,7 +702,7 @@
         <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>104102525845</v>
+        <v>110235700990</v>
       </c>
       <c r="P3" t="n">
         <v>8600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 관련 사업 확장 및 인수합병 기대감으로 주가 급등 전망. 뉴로메가 비교 및 텐버거 가능성 언급하며 강한 긍정적 논조.</t>
+          <t>인수합병 및 뉴로메가 사례 비교를 통한 높은 기대감 표출. 10월 코스닥 최고 종목 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '인수합병', '텐버거']</t>
+          <t>['인수합병', '텐버거', '로봇주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10070</v>
+        <v>10020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.91%</t>
+          <t>'+13.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H4" t="n">
         <v>13.6</v>
@@ -794,7 +794,7 @@
         <v>14.37</v>
       </c>
       <c r="O4" t="n">
-        <v>67738475355</v>
+        <v>69472875450</v>
       </c>
       <c r="P4" t="n">
         <v>14350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국책사업 및 반도체 관련 호재 언급과 함께 주가 상승 기대감 표출. 다만, 데드캣 바운스 및 종가 급락 가능성 언급으로 불확실성 존재.</t>
+          <t>국책사업 반도체 부지 관련 언급 및 공시 내용 복잡성. 외인 매도 및 주가 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국책사업', '반도체', '박스권']</t>
+          <t>['국책사업', '반도체', '공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18300</v>
+        <v>18740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.75%</t>
+          <t>'+7.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>115838690030</v>
+        <v>120659748990</v>
       </c>
       <c r="P5" t="n">
         <v>28800</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 테마 관련 수혜주 언급에도 불구하고, 단일 계좌 및 투주 등으로 인한 주가 하락 가능성 경고. 매도 권유.</t>
+          <t>반도체 테마 관련주로 언급되나, 단일 계좌 및 패턴 불안정성으로 인한 급락 가능성 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '단일계좌', '투주']</t>
+          <t>['반도체', '단일계좌', '음봉패턴']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13590</v>
+        <v>65000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.06%</t>
+          <t>'+2.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>145</v>
+        <v>324</v>
       </c>
       <c r="H6" t="n">
-        <v>3.42</v>
+        <v>22.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13060</v>
+        <v>63300</v>
       </c>
       <c r="K6" t="n">
-        <v>13390</v>
+        <v>63900</v>
       </c>
       <c r="L6" t="n">
-        <v>13620</v>
+        <v>65700</v>
       </c>
       <c r="M6" t="n">
-        <v>12910</v>
+        <v>63500</v>
       </c>
       <c r="N6" t="n">
-        <v>3.21</v>
+        <v>22.11</v>
       </c>
       <c r="O6" t="n">
-        <v>27450541610</v>
+        <v>65563261850</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>1640</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>-48000</v>
+        <v>64000</v>
       </c>
       <c r="S6" t="n">
-        <v>-12000</v>
+        <v>5000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>야간선물 및 미국장 반등, 광통신 테마 수혜 기대감 언급. 다만, 한국 증시 문제점 및 미장 약세 관련 언급으로 불확실성 존재.</t>
+          <t>원전 관련 기대감 속 주가 부진 및 3분기 매출 하회 관련 뉴스 언급. 외국계 증권사 매도세 포착.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '수주']</t>
+          <t>['원전', '매출', '외국계']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15150</v>
+        <v>13380</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.27%</t>
+          <t>'+2.45%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="H7" t="n">
-        <v>9.779999999999999</v>
+        <v>3.42</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14670</v>
+        <v>13060</v>
       </c>
       <c r="K7" t="n">
-        <v>14800</v>
+        <v>13390</v>
       </c>
       <c r="L7" t="n">
-        <v>15270</v>
+        <v>13620</v>
       </c>
       <c r="M7" t="n">
-        <v>14800</v>
+        <v>12910</v>
       </c>
       <c r="N7" t="n">
-        <v>9.710000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="O7" t="n">
-        <v>16395906235</v>
+        <v>29330693440</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R7" t="n">
-        <v>-47000</v>
+        <v>-48000</v>
       </c>
       <c r="S7" t="n">
-        <v>10000</v>
+        <v>-12000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 주가 조작 관련 의혹 제기가 반복적으로 나타남. 뱅크런 및 사모펀드 점검 관련 언급으로 시장 불안감 표출.</t>
+          <t>야간선물 및 미국장 반등, 광통신 테마 수혜 기대감 언급. 다만, 한국 증시 문제점 및 미장 약세 관련 언급으로 불확실성 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가조작', '이재명', '뱅크런']</t>
+          <t>['광통신', '야간선물', '수주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65300</v>
+        <v>15020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.16%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="H8" t="n">
-        <v>22.1</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>63300</v>
+        <v>14670</v>
       </c>
       <c r="K8" t="n">
-        <v>63900</v>
+        <v>14800</v>
       </c>
       <c r="L8" t="n">
-        <v>65700</v>
+        <v>15270</v>
       </c>
       <c r="M8" t="n">
-        <v>63500</v>
+        <v>14800</v>
       </c>
       <c r="N8" t="n">
-        <v>22.11</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>62489149500</v>
+        <v>17552766500</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>64000</v>
+        <v>-47000</v>
       </c>
       <c r="S8" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뉴스케일파워 등 관련 뉴스와 함께 주가 상승 기대감 표출. 다만, 3분기 매출 하회 및 외국계 증권사 매도 관련 언급으로 불확실성 존재.</t>
+          <t>정치적 이슈 및 주가 조작 의혹 강하게 제기. 금감원 사모펀드 점검 및 뱅크런 우려 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '원전주', '매출하회']</t>
+          <t>['주가조작', '정치', '뱅크런']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>216000</v>
+        <v>23750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.86%</t>
+          <t>'+2.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.18</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>1255</v>
+        <v>226</v>
       </c>
       <c r="H9" t="n">
-        <v>45.98</v>
+        <v>9.23</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>210000</v>
+        <v>23200</v>
       </c>
       <c r="K9" t="n">
-        <v>215000</v>
+        <v>23250</v>
       </c>
       <c r="L9" t="n">
-        <v>217500</v>
+        <v>24250</v>
       </c>
       <c r="M9" t="n">
-        <v>210500</v>
+        <v>22900</v>
       </c>
       <c r="N9" t="n">
-        <v>46.16</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1245480082000</v>
+        <v>25651970650</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>24950</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>17910</v>
       </c>
       <c r="R9" t="n">
-        <v>-865000</v>
+        <v>198000</v>
       </c>
       <c r="S9" t="n">
-        <v>111000</v>
+        <v>-21000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 노조 관련 언급이 주를 이루며, 주가 하락에 대한 부정적 전망과 개미 투자자들의 불안 심리 반영. 외인 매도세 지속 우려.</t>
+          <t>3분기 영업이익 1조원 돌파 기대감 및 운항 수익 급등 관련 뉴스 인용. 외인 매수세 일부 유입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['이재명', '외인매도', '주주제도']</t>
+          <t>['영업이익', '운항수익', '외인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1294000</v>
+        <v>214750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.26%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="E10" t="n">
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>553</v>
+        <v>498</v>
       </c>
       <c r="G10" t="n">
-        <v>1280</v>
+        <v>1149</v>
       </c>
       <c r="H10" t="n">
-        <v>48.85</v>
+        <v>45.98</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1262000</v>
+        <v>210000</v>
       </c>
       <c r="K10" t="n">
-        <v>1290000</v>
+        <v>215000</v>
       </c>
       <c r="L10" t="n">
-        <v>1308000</v>
+        <v>217500</v>
       </c>
       <c r="M10" t="n">
-        <v>1247000</v>
+        <v>210500</v>
       </c>
       <c r="N10" t="n">
-        <v>49.02</v>
+        <v>46.16</v>
       </c>
       <c r="O10" t="n">
-        <v>2188369515500</v>
+        <v>1320512675750</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>420500</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-291000</v>
+        <v>-865000</v>
       </c>
       <c r="S10" t="n">
-        <v>58000</v>
+        <v>111000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 주가 하락에 대한 부정적 전망 강하게 제기. 솔리다임 관련 언급과 함께 오너 리스크 부각.</t>
+          <t>정치적 논쟁 및 외인 매도 관련 언급. AI 산업 시작 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['이재명', '솔리다임', '오너리스크']</t>
+          <t>['AI', '외인매도', '정치']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15200</v>
+        <v>1285000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+1.82%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>549</v>
       </c>
       <c r="G11" t="n">
-        <v>122</v>
+        <v>1213</v>
       </c>
       <c r="H11" t="n">
-        <v>0.11</v>
+        <v>48.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14940</v>
+        <v>1262000</v>
       </c>
       <c r="K11" t="n">
-        <v>14940</v>
+        <v>1290000</v>
       </c>
       <c r="L11" t="n">
-        <v>16290</v>
+        <v>1308000</v>
       </c>
       <c r="M11" t="n">
-        <v>14330</v>
+        <v>1247000</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>49.02</v>
       </c>
       <c r="O11" t="n">
-        <v>31737012710</v>
+        <v>2348124750000</v>
       </c>
       <c r="P11" t="n">
-        <v>30800</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>9810</v>
+        <v>420500</v>
       </c>
       <c r="R11" t="n">
-        <v>19000</v>
+        <v>-291000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>코넥스 상장 사기 의혹 제기, 무능한 경영진 비판 및 주가 급락 기원.</t>
+          <t>정치적 이슈와 연계된 부정적 전망 및 주가 하락에 대한 불만. 외인 매수 부재 지적.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['상장 사기', '경영진', '주가 급락']</t>
+          <t>['정치', '외인', '주가하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41250</v>
+        <v>15060</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>645</v>
+        <v>115</v>
       </c>
       <c r="H12" t="n">
-        <v>12.97</v>
+        <v>0.11</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>40750</v>
+        <v>14940</v>
       </c>
       <c r="K12" t="n">
-        <v>40600</v>
+        <v>14940</v>
       </c>
       <c r="L12" t="n">
-        <v>41450</v>
+        <v>16290</v>
       </c>
       <c r="M12" t="n">
-        <v>40050</v>
+        <v>14330</v>
       </c>
       <c r="N12" t="n">
-        <v>12.84</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6317045550</v>
+        <v>34037064050</v>
       </c>
       <c r="P12" t="n">
-        <v>69200</v>
+        <v>30800</v>
       </c>
       <c r="Q12" t="n">
-        <v>24150</v>
+        <v>9810</v>
       </c>
       <c r="R12" t="n">
-        <v>-4000</v>
+        <v>19000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>HLB 담관암 FDA 승인 기대감 속, 진양곤 회장 및 경영진에 대한 불신 존재.</t>
+          <t>상장사기 의혹 및 경영진 사퇴 요구. 공모가 대비 현저히 낮은 시총과 주가 흐름에 대한 비판 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['FDA 승인', '담관암', '진양곤 회장']</t>
+          <t>['상장사기', '주가조작', '경영진']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20400</v>
+        <v>41050</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.5</v>
+        <v>0.13</v>
       </c>
       <c r="E13" t="n">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="G13" t="n">
-        <v>154</v>
+        <v>706</v>
       </c>
       <c r="H13" t="n">
-        <v>4.28</v>
+        <v>12.97</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>20750</v>
+        <v>40750</v>
       </c>
       <c r="K13" t="n">
-        <v>20500</v>
+        <v>40600</v>
       </c>
       <c r="L13" t="n">
-        <v>21500</v>
+        <v>41450</v>
       </c>
       <c r="M13" t="n">
-        <v>19440</v>
+        <v>40050</v>
       </c>
       <c r="N13" t="n">
-        <v>1.78</v>
+        <v>12.84</v>
       </c>
       <c r="O13" t="n">
-        <v>29725690375</v>
+        <v>6546478200</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q13" t="n">
-        <v>6320</v>
+        <v>24150</v>
       </c>
       <c r="R13" t="n">
-        <v>20000</v>
+        <v>-4000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>라온시큐어, 보안 이슈 속 신규 납품 요청 및 연기금 매수세 기대, 목표가 제시.</t>
+          <t>FDA 승인 기대감 속 주가 상승 전망. 외인 매수세 유입 및 야간 선물 급등, 미선물 동향 분석.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['보안', '납품 요청', '연기금']</t>
+          <t>['FDA승인', '외인매수', '주가전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28050</v>
+        <v>20150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-2.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.19</v>
+        <v>2.5</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="H14" t="n">
-        <v>53.59</v>
+        <v>4.28</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>29450</v>
+        <v>20750</v>
       </c>
       <c r="K14" t="n">
-        <v>29450</v>
+        <v>20500</v>
       </c>
       <c r="L14" t="n">
-        <v>29600</v>
+        <v>21500</v>
       </c>
       <c r="M14" t="n">
-        <v>27600</v>
+        <v>19440</v>
       </c>
       <c r="N14" t="n">
-        <v>26.75</v>
+        <v>1.78</v>
       </c>
       <c r="O14" t="n">
-        <v>55431561625</v>
+        <v>31572564325</v>
       </c>
       <c r="P14" t="n">
-        <v>32500</v>
+        <v>22450</v>
       </c>
       <c r="Q14" t="n">
-        <v>21000</v>
+        <v>6320</v>
       </c>
       <c r="R14" t="n">
-        <v>-9000</v>
+        <v>20000</v>
       </c>
       <c r="S14" t="n">
-        <v>-57000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 급락 및 외인 매도 시작에 대한 우려 제기. 유튜버 및 타인 의견 불신하며 매도 권유.</t>
+          <t>신규 납품 요청 및 보안 관련 뉴스 기반 주가 상승 기대. 연기금 매수세 유입 및 외인 매도 동향 분석.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,18 +1739,110 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적발표', '외인매도', '폭락']</t>
+          <t>['신규납품', '보안', '연기금']</t>
         </is>
       </c>
       <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>27550</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-6.45%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E15" t="n">
+        <v>49</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>191</v>
+      </c>
+      <c r="H15" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>29450</v>
+      </c>
+      <c r="K15" t="n">
+        <v>29450</v>
+      </c>
+      <c r="L15" t="n">
+        <v>29600</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27500</v>
+      </c>
+      <c r="N15" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>65890206075</v>
+      </c>
+      <c r="P15" t="n">
+        <v>32500</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>21000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-57000</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>실적 발표 후 주가 하락 및 외인 매도 지속. 유투버 및 개인 투자자 동향에 대한 불신.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['실적', '외인매도', '주가하락']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>1</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>003490</t>
         </is>

--- a/data/trending_integrated_20261016_10.xlsx
+++ b/data/trending_integrated_20261016_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H2" t="n">
         <v>0.73</v>
@@ -610,7 +610,7 @@
         <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>58948698370</v>
+        <v>59804109935</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 호재 및 정치적 불확실성 언급. 호남 반도체 관련주 동반 상승 가능성 제기.</t>
+          <t>군공항 이전 관련 이슈와 함께 호남 반도체 관련주 동반 상승 기대감. 일부 투자자는 신고가 돌파 및 8만원 가능성을 언급하며 매수 의견 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['군공항', '호남반도체', '정치']</t>
+          <t>['군공항', '호남반도체', '신고가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8430</v>
+        <v>8530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.90%</t>
+          <t>'+19.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H3" t="n">
         <v>0.72</v>
@@ -702,7 +702,7 @@
         <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>110235700990</v>
+        <v>119206268795</v>
       </c>
       <c r="P3" t="n">
         <v>8600</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>인수합병 및 뉴로메가 사례 비교를 통한 높은 기대감 표출. 10월 코스닥 최고 종목 가능성 언급.</t>
+          <t>인수합병 기대감 및 과거 뉴로메가 사례 비교 언급. 10월 코스닥 최고 종목 가능성, 신고가 경신 및 10만원 가능성 제시. 실적 기반 로봇주로서의 잠재력 부각.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수합병', '텐버거', '로봇주']</t>
+          <t>['인수합병', '로봇주', '신고가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>우리로</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10020</v>
+        <v>8070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.35%</t>
+          <t>'+12.87%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.77</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="H4" t="n">
-        <v>13.6</v>
+        <v>0.47</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8840</v>
+        <v>7150</v>
       </c>
       <c r="K4" t="n">
-        <v>9030</v>
+        <v>8100</v>
       </c>
       <c r="L4" t="n">
-        <v>10690</v>
+        <v>8430</v>
       </c>
       <c r="M4" t="n">
-        <v>8610</v>
+        <v>7810</v>
       </c>
       <c r="N4" t="n">
-        <v>14.37</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>69472875450</v>
+        <v>24127097585</v>
       </c>
       <c r="P4" t="n">
-        <v>14350</v>
+        <v>16200</v>
       </c>
       <c r="Q4" t="n">
-        <v>465</v>
+        <v>1206</v>
       </c>
       <c r="R4" t="n">
-        <v>-110000</v>
+        <v>-39000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국책사업 반도체 부지 관련 언급 및 공시 내용 복잡성. 외인 매도 및 주가 하락 가능성 제기.</t>
+          <t>데이터센터향 매출 발생 가능성 언급, 중국 및 미국 양자컴 관련 계약 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국책사업', '반도체', '공시']</t>
+          <t>['데이터센터', '양자컴퓨터', '매출']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>046970</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18740</v>
+        <v>9890</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.27%</t>
+          <t>'+11.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>17470</v>
+        <v>8840</v>
       </c>
       <c r="K5" t="n">
-        <v>18710</v>
+        <v>9030</v>
       </c>
       <c r="L5" t="n">
-        <v>20300</v>
+        <v>10690</v>
       </c>
       <c r="M5" t="n">
-        <v>17630</v>
+        <v>8610</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>120659748990</v>
+        <v>70702262550</v>
       </c>
       <c r="P5" t="n">
-        <v>28800</v>
+        <v>14350</v>
       </c>
       <c r="Q5" t="n">
-        <v>15780</v>
+        <v>465</v>
       </c>
       <c r="R5" t="n">
-        <v>16000</v>
+        <v>-110000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 테마 관련주로 언급되나, 단일 계좌 및 패턴 불안정성으로 인한 급락 가능성 제기.</t>
+          <t>국책사업 반도체 부지 조성 기대감 속 박스권 등락과 함께 금요일 종가 급락 및 하한가 예측. 일부 투자자는 호남 반도체 클러스터 시작을 주장하며 홀딩 의사 표명.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '단일계좌', '음봉패턴']</t>
+          <t>['국책사업', '반도체', '호남']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65000</v>
+        <v>18720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.69%</t>
+          <t>'+7.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G6" t="n">
-        <v>324</v>
+        <v>199</v>
       </c>
       <c r="H6" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>63300</v>
+        <v>17470</v>
       </c>
       <c r="K6" t="n">
-        <v>63900</v>
+        <v>18710</v>
       </c>
       <c r="L6" t="n">
-        <v>65700</v>
+        <v>20300</v>
       </c>
       <c r="M6" t="n">
-        <v>63500</v>
+        <v>17630</v>
       </c>
       <c r="N6" t="n">
-        <v>22.11</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>65563261850</v>
+        <v>126092770290</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>28800</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>15780</v>
       </c>
       <c r="R6" t="n">
-        <v>64000</v>
+        <v>16000</v>
       </c>
       <c r="S6" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 속 주가 부진 및 3분기 매출 하회 관련 뉴스 언급. 외국계 증권사 매도세 포착.</t>
+          <t>일본 및 호남 메가 반도체 공장 수혜주로 언급되었으나, 단일계좌 투매 및 급락 패턴 지속. 저항대 돌파 실패 시 추가 하락 가능성 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['원전', '매출', '외국계']</t>
+          <t>['반도체', '단일계좌', '급락']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,178 +1016,178 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13380</v>
+        <v>10420</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.45%</t>
+          <t>'+4.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="H7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13060</v>
+        <v>9930</v>
       </c>
       <c r="K7" t="n">
-        <v>13390</v>
+        <v>10100</v>
       </c>
       <c r="L7" t="n">
-        <v>13620</v>
+        <v>11100</v>
       </c>
       <c r="M7" t="n">
-        <v>12910</v>
+        <v>9860</v>
       </c>
       <c r="N7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>29330693440</v>
+        <v>28381662535</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>19380</v>
       </c>
       <c r="Q7" t="n">
-        <v>1640</v>
+        <v>3200</v>
       </c>
       <c r="R7" t="n">
-        <v>-48000</v>
+        <v>-160000</v>
       </c>
       <c r="S7" t="n">
-        <v>-12000</v>
+        <v>-2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>야간선물 및 미국장 반등, 광통신 테마 수혜 기대감 언급. 다만, 한국 증시 문제점 및 미장 약세 관련 언급으로 불확실성 존재.</t>
+          <t>뉴스 언급에도 불구하고 기관 및 외국인 매수세가 매도로 전환되며 주가 상승 정체. 투자자들은 '개잡주'라 칭하며 부정적 전망 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '수주']</t>
+          <t>['기관매수', '외국인매도', '개잡주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15020</v>
+        <v>13480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="H8" t="n">
-        <v>9.779999999999999</v>
+        <v>3.42</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14670</v>
+        <v>13060</v>
       </c>
       <c r="K8" t="n">
-        <v>14800</v>
+        <v>13390</v>
       </c>
       <c r="L8" t="n">
-        <v>15270</v>
+        <v>13620</v>
       </c>
       <c r="M8" t="n">
-        <v>14800</v>
+        <v>12910</v>
       </c>
       <c r="N8" t="n">
-        <v>9.710000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="O8" t="n">
-        <v>17552766500</v>
+        <v>30326628560</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>1640</v>
       </c>
       <c r="R8" t="n">
-        <v>-47000</v>
+        <v>-48000</v>
       </c>
       <c r="S8" t="n">
-        <v>10000</v>
+        <v>-12000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 주가 조작 의혹 강하게 제기. 금감원 사모펀드 점검 및 뱅크런 우려 언급.</t>
+          <t>야간선물 및 미국장 반등, 광통신 테마 수혜 기대감 언급. 다만, 한국 증시 문제점 및 미장 약세 관련 언급으로 불확실성 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가조작', '정치', '뱅크런']</t>
+          <t>['광통신', '야간선물', '수주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23750</v>
+        <v>23800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+2.59%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H9" t="n">
         <v>9.23</v>
@@ -1254,7 +1254,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>25651970650</v>
+        <v>26484604225</v>
       </c>
       <c r="P9" t="n">
         <v>24950</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 영업이익 1조원 돌파 기대감 및 운항 수익 급등 관련 뉴스 인용. 외인 매수세 일부 유입.</t>
+          <t>3분기 영업이익 1조원 돌파 기대감 속 초대형 유조선 운항수익 급등 뉴스 언급. 코스피 선물 상승과 함께 주가 상승 전망 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업이익', '운항수익', '외인']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214750</v>
+        <v>1294000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.26%</t>
+          <t>'+2.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="E10" t="n">
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>498</v>
+        <v>542</v>
       </c>
       <c r="G10" t="n">
-        <v>1149</v>
+        <v>1240</v>
       </c>
       <c r="H10" t="n">
-        <v>45.98</v>
+        <v>48.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>210000</v>
+        <v>1262000</v>
       </c>
       <c r="K10" t="n">
-        <v>215000</v>
+        <v>1290000</v>
       </c>
       <c r="L10" t="n">
-        <v>217500</v>
+        <v>1308000</v>
       </c>
       <c r="M10" t="n">
-        <v>210500</v>
+        <v>1247000</v>
       </c>
       <c r="N10" t="n">
-        <v>46.16</v>
+        <v>49.02</v>
       </c>
       <c r="O10" t="n">
-        <v>1320512675750</v>
+        <v>2517397102000</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>420500</v>
       </c>
       <c r="R10" t="n">
-        <v>-865000</v>
+        <v>-291000</v>
       </c>
       <c r="S10" t="n">
-        <v>111000</v>
+        <v>58000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 논쟁 및 외인 매도 관련 언급. AI 산업 시작 가능성 언급.</t>
+          <t>정치적 이슈와 연관된 '전라닉스 리스크' 언급 및 '가짜 반등'에 대한 경고. 주가 부진과 외인 매도세에 대한 부정적 의견 지배적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI', '외인매도', '정치']</t>
+          <t>['전라닉스', '가짜반등', '외인매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1285000</v>
+        <v>64900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.82%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.17</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>107</v>
       </c>
       <c r="F11" t="n">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>1213</v>
+        <v>327</v>
       </c>
       <c r="H11" t="n">
-        <v>48.85</v>
+        <v>22.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1262000</v>
+        <v>63300</v>
       </c>
       <c r="K11" t="n">
-        <v>1290000</v>
+        <v>63900</v>
       </c>
       <c r="L11" t="n">
-        <v>1308000</v>
+        <v>65700</v>
       </c>
       <c r="M11" t="n">
-        <v>1247000</v>
+        <v>63500</v>
       </c>
       <c r="N11" t="n">
-        <v>49.02</v>
+        <v>22.11</v>
       </c>
       <c r="O11" t="n">
-        <v>2348124750000</v>
+        <v>68400167300</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>420500</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>-291000</v>
+        <v>64000</v>
       </c>
       <c r="S11" t="n">
-        <v>58000</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 전망 및 주가 하락에 대한 불만. 외인 매수 부재 지적.</t>
+          <t>뉴스케일파워 상승 언급에도 불구하고 주가 흐름 정체 및 음전 가능성 제기. 3분기 매출 하회 소식에 대한 불만과 신뢰도 하락 지적.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '외인', '주가하락']</t>
+          <t>['뉴스케일파워', '매출하회', '신뢰도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15060</v>
+        <v>215000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+2.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>504</v>
       </c>
       <c r="G12" t="n">
-        <v>115</v>
+        <v>1109</v>
       </c>
       <c r="H12" t="n">
-        <v>0.11</v>
+        <v>45.98</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14940</v>
+        <v>210000</v>
       </c>
       <c r="K12" t="n">
-        <v>14940</v>
+        <v>215000</v>
       </c>
       <c r="L12" t="n">
-        <v>16290</v>
+        <v>217500</v>
       </c>
       <c r="M12" t="n">
-        <v>14330</v>
+        <v>210500</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>46.16</v>
       </c>
       <c r="O12" t="n">
-        <v>34037064050</v>
+        <v>1402419175250</v>
       </c>
       <c r="P12" t="n">
-        <v>30800</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>9810</v>
+        <v>94500</v>
       </c>
       <c r="R12" t="n">
-        <v>19000</v>
+        <v>-865000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>상장사기 의혹 및 경영진 사퇴 요구. 공모가 대비 현저히 낮은 시총과 주가 흐름에 대한 비판 제기.</t>
+          <t>정치적 이슈와 관련된 논란 속에서 주가 하락에 대한 우려 표출. 외인 매도세 및 정부 정책에 대한 비판적 시각 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['상장사기', '주가조작', '경영진']</t>
+          <t>['이재명', '외인매도', '정부정책']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41050</v>
+        <v>14950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+1.91%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="F13" t="n">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>706</v>
+        <v>108</v>
       </c>
       <c r="H13" t="n">
-        <v>12.97</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>40750</v>
+        <v>14670</v>
       </c>
       <c r="K13" t="n">
-        <v>40600</v>
+        <v>14800</v>
       </c>
       <c r="L13" t="n">
-        <v>41450</v>
+        <v>15270</v>
       </c>
       <c r="M13" t="n">
-        <v>40050</v>
+        <v>14800</v>
       </c>
       <c r="N13" t="n">
-        <v>12.84</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>6546478200</v>
+        <v>18978769580</v>
       </c>
       <c r="P13" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-4000</v>
+        <v>-47000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감 속 주가 상승 전망. 외인 매수세 유입 및 야간 선물 급등, 미선물 동향 분석.</t>
+          <t>정치적 이슈 및 주가 조작 의혹 강하게 제기. 금감원 사모펀드 점검 및 뱅크런 우려 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['FDA승인', '외인매수', '주가전망']</t>
+          <t>['주가조작', '정치', '뱅크런']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20150</v>
+        <v>41150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.89%</t>
+          <t>'+0.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.5</v>
+        <v>0.13</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="G14" t="n">
-        <v>159</v>
+        <v>713</v>
       </c>
       <c r="H14" t="n">
-        <v>4.28</v>
+        <v>12.97</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>20750</v>
+        <v>40750</v>
       </c>
       <c r="K14" t="n">
-        <v>20500</v>
+        <v>40600</v>
       </c>
       <c r="L14" t="n">
-        <v>21500</v>
+        <v>41450</v>
       </c>
       <c r="M14" t="n">
-        <v>19440</v>
+        <v>40050</v>
       </c>
       <c r="N14" t="n">
-        <v>1.78</v>
+        <v>12.84</v>
       </c>
       <c r="O14" t="n">
-        <v>31572564325</v>
+        <v>6779184950</v>
       </c>
       <c r="P14" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q14" t="n">
-        <v>6320</v>
+        <v>24150</v>
       </c>
       <c r="R14" t="n">
-        <v>20000</v>
+        <v>-4000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신규 납품 요청 및 보안 관련 뉴스 기반 주가 상승 기대. 연기금 매수세 유입 및 외인 매도 동향 분석.</t>
+          <t>담관암 FDA 승인 기대감 속 외인 매수세 유입, 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신규납품', '보안', '연기금']</t>
+          <t>['FDA 승인', '외인 매수', '담관암']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,86 +1752,86 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27550</v>
+        <v>14980</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.45%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="H15" t="n">
-        <v>53.5</v>
+        <v>0.11</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29450</v>
+        <v>14940</v>
       </c>
       <c r="K15" t="n">
-        <v>29450</v>
+        <v>14940</v>
       </c>
       <c r="L15" t="n">
-        <v>29600</v>
+        <v>16290</v>
       </c>
       <c r="M15" t="n">
-        <v>27500</v>
+        <v>14330</v>
       </c>
       <c r="N15" t="n">
-        <v>26.75</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>65890206075</v>
+        <v>34757988985</v>
       </c>
       <c r="P15" t="n">
-        <v>32500</v>
+        <v>30800</v>
       </c>
       <c r="Q15" t="n">
-        <v>21000</v>
+        <v>9810</v>
       </c>
       <c r="R15" t="n">
-        <v>-9000</v>
+        <v>19000</v>
       </c>
       <c r="S15" t="n">
-        <v>-57000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락 및 외인 매도 지속. 유투버 및 개인 투자자 동향에 대한 불신.</t>
+          <t>상장 사기 의혹 제기, 경영진 사퇴 요구 및 공모자금 관련 논란.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '외인매도', '주가하락']</t>
+          <t>['상장 사기', '경영진', '공모자금']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1843,6 +1843,190 @@
         </is>
       </c>
       <c r="Z15" t="inlineStr">
+        <is>
+          <t>250030</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>20150</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-2.89%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>61</v>
+      </c>
+      <c r="F16" t="n">
+        <v>47</v>
+      </c>
+      <c r="G16" t="n">
+        <v>171</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>20750</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20500</v>
+      </c>
+      <c r="L16" t="n">
+        <v>21500</v>
+      </c>
+      <c r="M16" t="n">
+        <v>19440</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O16" t="n">
+        <v>31943139075</v>
+      </c>
+      <c r="P16" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6320</v>
+      </c>
+      <c r="R16" t="n">
+        <v>20000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>금융권 보안 취약점 부각 속 신규 납품 요청 및 러브콜, 보안주로서의 상승 기대.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['보안', '금융권', '납품']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>27650</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-6.11%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E17" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" t="n">
+        <v>46</v>
+      </c>
+      <c r="G17" t="n">
+        <v>239</v>
+      </c>
+      <c r="H17" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>29450</v>
+      </c>
+      <c r="K17" t="n">
+        <v>29450</v>
+      </c>
+      <c r="L17" t="n">
+        <v>29600</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27500</v>
+      </c>
+      <c r="N17" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>69072878125</v>
+      </c>
+      <c r="P17" t="n">
+        <v>32500</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>21000</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-57000</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>실적 발표 이후 외국인 매도세 본격화 및 주가 급락. 유튜버 발언 불신, 일봉 차트 붕괴에 대한 우려와 함께 매도 의견 대두.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['실적발표', '외국인매도', '주가급락']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>003490</t>
         </is>

--- a/data/trending_integrated_20261016_10.xlsx
+++ b/data/trending_integrated_20261016_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8080</v>
+        <v>7940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+22.98%</t>
+          <t>'+20.85%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H2" t="n">
         <v>0.73</v>
@@ -610,7 +610,7 @@
         <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>59804109935</v>
+        <v>62437948440</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 이슈와 함께 호남 반도체 관련주 동반 상승 기대감. 일부 투자자는 신고가 돌파 및 8만원 가능성을 언급하며 매수 의견 제시.</t>
+          <t>군 공항 이전 관련 정치권 언급 속 투기성 거래 포착. 호남 관련주 및 반도체 테마 동반 상승 가능성 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['군공항', '호남반도체', '신고가']</t>
+          <t>['군공항 이전', '투기성 거래', '호남 관련주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8530</v>
+        <v>8540</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.30%</t>
+          <t>'+19.44%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="H3" t="n">
         <v>0.72</v>
@@ -693,7 +693,7 @@
         <v>7430</v>
       </c>
       <c r="L3" t="n">
-        <v>8600</v>
+        <v>8650</v>
       </c>
       <c r="M3" t="n">
         <v>7300</v>
@@ -702,10 +702,10 @@
         <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>119206268795</v>
+        <v>127713158190</v>
       </c>
       <c r="P3" t="n">
-        <v>8600</v>
+        <v>8650</v>
       </c>
       <c r="Q3" t="n">
         <v>2270</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>인수합병 기대감 및 과거 뉴로메가 사례 비교 언급. 10월 코스닥 최고 종목 가능성, 신고가 경신 및 10만원 가능성 제시. 실적 기반 로봇주로서의 잠재력 부각.</t>
+          <t>인수합병 및 뉴로메가 편입 사례 비교. 텐버거 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인수합병', '로봇주', '신고가']</t>
+          <t>['인수합병', '텐버거', '뉴로메가']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8070</v>
+        <v>8420</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.87%</t>
+          <t>'+17.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H4" t="n">
         <v>0.47</v>
@@ -785,7 +785,7 @@
         <v>8100</v>
       </c>
       <c r="L4" t="n">
-        <v>8430</v>
+        <v>8500</v>
       </c>
       <c r="M4" t="n">
         <v>7810</v>
@@ -794,7 +794,7 @@
         <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>24127097585</v>
+        <v>29274885840</v>
       </c>
       <c r="P4" t="n">
         <v>16200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>데이터센터향 매출 발생 가능성 언급, 중국 및 미국 양자컴 관련 계약 기대.</t>
+          <t>데이터 센터향 매출 및 중국 시장 개방 기대감 속 미국 양자컴퓨터 관련주로 분류. SPAD 200 미반영 및 9천원대 매물 소화 과제.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['데이터센터', '양자컴퓨터', '매출']</t>
+          <t>['데이터 센터', '양자컴퓨터', '매물 소화']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9890</v>
+        <v>9630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.88%</t>
+          <t>'+8.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.77</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H5" t="n">
         <v>13.6</v>
@@ -886,7 +886,7 @@
         <v>14.37</v>
       </c>
       <c r="O5" t="n">
-        <v>70702262550</v>
+        <v>73960450895</v>
       </c>
       <c r="P5" t="n">
         <v>14350</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국책사업 반도체 부지 조성 기대감 속 박스권 등락과 함께 금요일 종가 급락 및 하한가 예측. 일부 투자자는 호남 반도체 클러스터 시작을 주장하며 홀딩 의사 표명.</t>
+          <t>국책사업 반도체 부지 관련 홀딩 기대감. 주포 장난질 의혹 및 재료 식음 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국책사업', '반도체', '호남']</t>
+          <t>['국책사업', '반도체', '주포']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18720</v>
+        <v>18830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.16%</t>
+          <t>'+7.78%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G6" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>126092770290</v>
+        <v>131178275315</v>
       </c>
       <c r="P6" t="n">
         <v>28800</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>일본 및 호남 메가 반도체 공장 수혜주로 언급되었으나, 단일계좌 투매 및 급락 패턴 지속. 저항대 돌파 실패 시 추가 하락 가능성 제기.</t>
+          <t>반도체 테마 관련주로 일본 및 호남 반도체 공장 수혜 기대. 단일 계좌 투기 과열 종목 지정 및 급락 패턴 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반도체', '단일계좌', '급락']</t>
+          <t>['반도체 테마', '수혜주', '단일 계좌']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10420</v>
+        <v>10320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.93%</t>
+          <t>'+3.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>28381662535</v>
+        <v>29033725390</v>
       </c>
       <c r="P7" t="n">
         <v>19380</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>뉴스 언급에도 불구하고 기관 및 외국인 매수세가 매도로 전환되며 주가 상승 정체. 투자자들은 '개잡주'라 칭하며 부정적 전망 제시.</t>
+          <t>뉴스 노출에도 불구하고 주가 부진 지속. 외인 매수 후 매도 추정.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관매수', '외국인매도', '개잡주']</t>
+          <t>['주가 부진', '기관 외국인', '매수 매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,175 +1115,175 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13480</v>
+        <v>18810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+3.52%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.21</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="H8" t="n">
-        <v>3.42</v>
+        <v>27.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13060</v>
+        <v>18170</v>
       </c>
       <c r="K8" t="n">
-        <v>13390</v>
+        <v>18340</v>
       </c>
       <c r="L8" t="n">
-        <v>13620</v>
+        <v>18990</v>
       </c>
       <c r="M8" t="n">
-        <v>12910</v>
+        <v>18110</v>
       </c>
       <c r="N8" t="n">
-        <v>3.21</v>
+        <v>27.82</v>
       </c>
       <c r="O8" t="n">
-        <v>30326628560</v>
+        <v>24946612225</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>35350</v>
       </c>
       <c r="Q8" t="n">
-        <v>1640</v>
+        <v>17210</v>
       </c>
       <c r="R8" t="n">
-        <v>-48000</v>
+        <v>84000</v>
       </c>
       <c r="S8" t="n">
-        <v>-12000</v>
+        <v>70000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>야간선물 및 미국장 반등, 광통신 테마 수혜 기대감 언급. 다만, 한국 증시 문제점 및 미장 약세 관련 언급으로 불확실성 존재.</t>
+          <t>미증시 반등 및 유가 상승에 따른 강한 반등 예상. FDC, FLNG 수주 임박.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '야간선물', '수주']</t>
+          <t>['미증시 반등', '수주 임박', '유가 상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23800</v>
+        <v>13500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.59%</t>
+          <t>'+3.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="H9" t="n">
-        <v>9.23</v>
+        <v>3.42</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>23200</v>
+        <v>13060</v>
       </c>
       <c r="K9" t="n">
-        <v>23250</v>
+        <v>13390</v>
       </c>
       <c r="L9" t="n">
-        <v>24250</v>
+        <v>13620</v>
       </c>
       <c r="M9" t="n">
-        <v>22900</v>
+        <v>12910</v>
       </c>
       <c r="N9" t="n">
-        <v>9.210000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="O9" t="n">
-        <v>26484604225</v>
+        <v>31237470750</v>
       </c>
       <c r="P9" t="n">
-        <v>24950</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>17910</v>
+        <v>1640</v>
       </c>
       <c r="R9" t="n">
-        <v>198000</v>
+        <v>-48000</v>
       </c>
       <c r="S9" t="n">
-        <v>-21000</v>
+        <v>-12000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 영업이익 1조원 돌파 기대감 속 초대형 유조선 운항수익 급등 뉴스 언급. 코스피 선물 상승과 함께 주가 상승 전망 제시.</t>
+          <t>야간 선물 폭등 및 미국 장 반등 속 광통신 테마 강세. 13490원 돌파 및 만원대 안착 기대감 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['운항수익', '영업이익', 'SCFI']</t>
+          <t>['광통신', '야간선물', '미국장 반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1294000</v>
+        <v>65300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+3.16%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.17</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>109</v>
       </c>
       <c r="F10" t="n">
-        <v>542</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>1240</v>
+        <v>341</v>
       </c>
       <c r="H10" t="n">
-        <v>48.85</v>
+        <v>22.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1262000</v>
+        <v>63300</v>
       </c>
       <c r="K10" t="n">
-        <v>1290000</v>
+        <v>63900</v>
       </c>
       <c r="L10" t="n">
-        <v>1308000</v>
+        <v>65700</v>
       </c>
       <c r="M10" t="n">
-        <v>1247000</v>
+        <v>63500</v>
       </c>
       <c r="N10" t="n">
-        <v>49.02</v>
+        <v>22.11</v>
       </c>
       <c r="O10" t="n">
-        <v>2517397102000</v>
+        <v>70205946500</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>420500</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-291000</v>
+        <v>64000</v>
       </c>
       <c r="S10" t="n">
-        <v>58000</v>
+        <v>5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 '전라닉스 리스크' 언급 및 '가짜 반등'에 대한 경고. 주가 부진과 외인 매도세에 대한 부정적 의견 지배적.</t>
+          <t>3분기 매출 하회 공시 및 주가 하락. 신뢰도 저하 및 외국계 매도.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['전라닉스', '가짜반등', '외인매도']</t>
+          <t>['매출 하회', '신뢰도', '외국계 매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64900</v>
+        <v>23800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+2.59%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>327</v>
+        <v>239</v>
       </c>
       <c r="H11" t="n">
-        <v>22.1</v>
+        <v>9.23</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>63300</v>
+        <v>23200</v>
       </c>
       <c r="K11" t="n">
-        <v>63900</v>
+        <v>23250</v>
       </c>
       <c r="L11" t="n">
-        <v>65700</v>
+        <v>24250</v>
       </c>
       <c r="M11" t="n">
-        <v>63500</v>
+        <v>22900</v>
       </c>
       <c r="N11" t="n">
-        <v>22.11</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>68400167300</v>
+        <v>27424855775</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>24950</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>17910</v>
       </c>
       <c r="R11" t="n">
-        <v>64000</v>
+        <v>198000</v>
       </c>
       <c r="S11" t="n">
-        <v>5000</v>
+        <v>-21000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 언급에도 불구하고 주가 흐름 정체 및 음전 가능성 제기. 3분기 매출 하회 소식에 대한 불만과 신뢰도 하락 지적.</t>
+          <t>운항수익 폭등 및 3분기 영업이익 1조원 돌파 기대. SCFI 최고치 경신.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '매출하회', '신뢰도']</t>
+          <t>['운항수익', '영업이익', 'SCFI']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>011200</t>
         </is>
       </c>
     </row>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G12" t="n">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="H12" t="n">
         <v>45.98</v>
@@ -1530,7 +1530,7 @@
         <v>46.16</v>
       </c>
       <c r="O12" t="n">
-        <v>1402419175250</v>
+        <v>1446698749750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 논란 속에서 주가 하락에 대한 우려 표출. 외인 매도세 및 정부 정책에 대한 비판적 시각 존재.</t>
+          <t>정치적 이슈와 연계된 부정적 투자 심리. AI 시작 기대감은 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['이재명', '외인매도', '정부정책']</t>
+          <t>['정치', 'AI', '투자심리']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14950</v>
+        <v>1292000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.91%</t>
+          <t>'+2.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>539</v>
       </c>
       <c r="G13" t="n">
-        <v>108</v>
+        <v>1296</v>
       </c>
       <c r="H13" t="n">
-        <v>9.779999999999999</v>
+        <v>48.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14670</v>
+        <v>1262000</v>
       </c>
       <c r="K13" t="n">
-        <v>14800</v>
+        <v>1290000</v>
       </c>
       <c r="L13" t="n">
-        <v>15270</v>
+        <v>1308000</v>
       </c>
       <c r="M13" t="n">
-        <v>14800</v>
+        <v>1247000</v>
       </c>
       <c r="N13" t="n">
-        <v>9.710000000000001</v>
+        <v>49.02</v>
       </c>
       <c r="O13" t="n">
-        <v>18978769580</v>
+        <v>2586446082000</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>420500</v>
       </c>
       <c r="R13" t="n">
-        <v>-47000</v>
+        <v>-291000</v>
       </c>
       <c r="S13" t="n">
-        <v>10000</v>
+        <v>58000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 주가 조작 의혹 강하게 제기. 금감원 사모펀드 점검 및 뱅크런 우려 언급.</t>
+          <t>정치적 리스크와 연계된 부정적 전망. 단기 반등 후 하락 추세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가조작', '정치', '뱅크런']</t>
+          <t>['정치 리스크', '하락 추세', '단기 반등']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>41150</v>
+        <v>14960</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+0.98%</t>
+          <t>'+1.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>173</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="G14" t="n">
-        <v>713</v>
+        <v>122</v>
       </c>
       <c r="H14" t="n">
-        <v>12.97</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>40750</v>
+        <v>14670</v>
       </c>
       <c r="K14" t="n">
-        <v>40600</v>
+        <v>14800</v>
       </c>
       <c r="L14" t="n">
-        <v>41450</v>
+        <v>15270</v>
       </c>
       <c r="M14" t="n">
-        <v>40050</v>
+        <v>14800</v>
       </c>
       <c r="N14" t="n">
-        <v>12.84</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>6779184950</v>
+        <v>19854455105</v>
       </c>
       <c r="P14" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-4000</v>
+        <v>-47000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 기대감 속 외인 매수세 유입, 주가 상승 전망.</t>
+          <t>정치적 이슈와 주가 조작 의혹 지속. 외인 보유율 관리 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['FDA 승인', '외인 매수', '담관암']</t>
+          <t>['주가 조작', '정치적 이슈', '외인 보유율']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14980</v>
+        <v>41300</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+1.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="E15" t="n">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="G15" t="n">
-        <v>121</v>
+        <v>739</v>
       </c>
       <c r="H15" t="n">
-        <v>0.11</v>
+        <v>12.97</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14940</v>
+        <v>40750</v>
       </c>
       <c r="K15" t="n">
-        <v>14940</v>
+        <v>40600</v>
       </c>
       <c r="L15" t="n">
-        <v>16290</v>
+        <v>41450</v>
       </c>
       <c r="M15" t="n">
-        <v>14330</v>
+        <v>40050</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>12.84</v>
       </c>
       <c r="O15" t="n">
-        <v>34757988985</v>
+        <v>7063982525</v>
       </c>
       <c r="P15" t="n">
-        <v>30800</v>
+        <v>69200</v>
       </c>
       <c r="Q15" t="n">
-        <v>9810</v>
+        <v>24150</v>
       </c>
       <c r="R15" t="n">
-        <v>19000</v>
+        <v>-4000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>상장 사기 의혹 제기, 경영진 사퇴 요구 및 공모자금 관련 논란.</t>
+          <t>담관암 FDA 승인 기대감 속 외인 매수세 유입, 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상장 사기', '경영진', '공모자금']</t>
+          <t>['FDA 승인', '외인 매수', '담관암']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20150</v>
+        <v>15010</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.89%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="H16" t="n">
-        <v>4.28</v>
+        <v>0.11</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>20750</v>
+        <v>14940</v>
       </c>
       <c r="K16" t="n">
-        <v>20500</v>
+        <v>14940</v>
       </c>
       <c r="L16" t="n">
-        <v>21500</v>
+        <v>16290</v>
       </c>
       <c r="M16" t="n">
-        <v>19440</v>
+        <v>14330</v>
       </c>
       <c r="N16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>31943139075</v>
+        <v>36078669700</v>
       </c>
       <c r="P16" t="n">
-        <v>22450</v>
+        <v>30800</v>
       </c>
       <c r="Q16" t="n">
-        <v>6320</v>
+        <v>9810</v>
       </c>
       <c r="R16" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금융권 보안 취약점 부각 속 신규 납품 요청 및 러브콜, 보안주로서의 상승 기대.</t>
+          <t>상장 사기 의혹 제기, 경영진 사퇴 요구 및 공모자금 관련 논란.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['보안', '금융권', '납품']</t>
+          <t>['상장 사기', '경영진', '공모자금']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,97 +1936,189 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27650</v>
+        <v>20000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.11%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.19</v>
+        <v>2.5</v>
       </c>
       <c r="E17" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="H17" t="n">
-        <v>53.49</v>
+        <v>4.28</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29450</v>
+        <v>20750</v>
       </c>
       <c r="K17" t="n">
-        <v>29450</v>
+        <v>20500</v>
       </c>
       <c r="L17" t="n">
-        <v>29600</v>
+        <v>21500</v>
       </c>
       <c r="M17" t="n">
-        <v>27500</v>
+        <v>19440</v>
       </c>
       <c r="N17" t="n">
-        <v>26.75</v>
+        <v>1.78</v>
       </c>
       <c r="O17" t="n">
-        <v>69072878125</v>
+        <v>32429155650</v>
       </c>
       <c r="P17" t="n">
-        <v>32500</v>
+        <v>22450</v>
       </c>
       <c r="Q17" t="n">
-        <v>21000</v>
+        <v>6320</v>
       </c>
       <c r="R17" t="n">
-        <v>-9000</v>
+        <v>20000</v>
       </c>
       <c r="S17" t="n">
-        <v>-57000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>실적 발표 이후 외국인 매도세 본격화 및 주가 급락. 유튜버 발언 불신, 일봉 차트 붕괴에 대한 우려와 함께 매도 의견 대두.</t>
+          <t>농협, KDB 등 금융권 신규 납품 요청 및 보안 강화 트렌드 속 수혜 기대. 해킹 사고 증가 추세 및 프로그램 매매 관련 이슈.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적발표', '외국인매도', '주가급락']</t>
+          <t>['보안', '신규 납품', '해킹 사고']</t>
         </is>
       </c>
       <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>042510</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>대한항공</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>27500</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-6.62%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" t="n">
+        <v>49</v>
+      </c>
+      <c r="G18" t="n">
+        <v>251</v>
+      </c>
+      <c r="H18" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>29450</v>
+      </c>
+      <c r="K18" t="n">
+        <v>29450</v>
+      </c>
+      <c r="L18" t="n">
+        <v>29600</v>
+      </c>
+      <c r="M18" t="n">
+        <v>27500</v>
+      </c>
+      <c r="N18" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>72771743000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>32500</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21000</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-57000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>실적 발표 후 외국인 매도 시작 및 주가 급락. 투자 심리 악화.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['실적 발표', '외국인 매도', '주가 급락']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
         <v>1</v>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>003490</t>
         </is>
